--- a/data/excel/sistemas_componentes.xlsx
+++ b/data/excel/sistemas_componentes.xlsx
@@ -56,6 +56,45 @@
   </x:si>
   <x:si>
     <x:t>FechaActualizacionUtc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIS-MOTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Motor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sistema</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAE_GM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:18:56.9642605Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:19:32.6636326Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUB-LUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lubricacion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Subsistema</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUBRICACION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T21:24:48.1544478Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -421,12 +460,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D1"/>
+  <x:dimension ref="A1:N3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.139196" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.567768" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="12.710625" style="0" customWidth="1"/>
@@ -436,8 +475,7 @@
     <x:col min="10" max="10" width="13.853482" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="9.139196" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="18.996339" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16.853482" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="20.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="14" width="28.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:14">
@@ -482,6 +520,61 @@
       </x:c>
       <x:c r="N1" s="1" t="s">
         <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
+      <x:c r="A2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
